--- a/assets/constructions/examples/ctd_bs_carte.xlsx
+++ b/assets/constructions/examples/ctd_bs_carte.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U6"/>
+  <dimension ref="A1:Y6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,11 +534,31 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DBCC120164-C</t>
+          <t>ABCC5566</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -548,16 +568,16 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>16.2</v>
+        <v>15.4</v>
       </c>
       <c r="E2" t="n">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="F2" t="n">
-        <v>164</v>
+        <v>66</v>
       </c>
       <c r="G2" t="n">
-        <v>106.5</v>
+        <v>46.5</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
@@ -566,18 +586,18 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>DER_D.CC120164-C</t>
+          <t>DER_A.CC:45/55</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>ISO_CC1204H</t>
+          <t>ISO_CC09T3H</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>CC1204H</t>
+          <t>CC09T3H</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -595,7 +615,7 @@
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>0.18</v>
+        <v>0.05</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -604,12 +624,26 @@
         <is>
           <t>2019 / DEREK Металлорежущий инструмент и оснастка 2019 RUS_Ver.1.01</t>
         </is>
+      </c>
+      <c r="V2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" t="n">
+        <v>89.34999999999999</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>7324.37</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DBCC2533-C</t>
+          <t>MRTP70110</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -619,16 +653,16 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>19.2</v>
+        <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="F3" t="n">
-        <v>33</v>
+        <v>110</v>
       </c>
       <c r="G3" t="n">
-        <v>20.9</v>
+        <v>66</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
@@ -637,18 +671,18 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>DER_D.CC2533-C</t>
+          <t>DER_FBH:63</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>ISO_CC0602H</t>
+          <t>ISO_TP1103H|ISO_TP1103RH</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>CC0602H</t>
+          <t>ISO_TP1103H|ISO_TP1103RH</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -658,7 +692,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>T</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -666,7 +700,7 @@
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>0.01</v>
+        <v>0.12</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -675,12 +709,26 @@
         <is>
           <t>2019 / DEREK Металлорежущий инструмент и оснастка 2019 RUS_Ver.1.01</t>
         </is>
+      </c>
+      <c r="V3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W3" t="n">
+        <v>127.65</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>10463.97</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AKCC5674</t>
+          <t>DBCC120164-C</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -690,16 +738,16 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>17</v>
+        <v>16.2</v>
       </c>
       <c r="E4" t="n">
-        <v>56</v>
+        <v>12</v>
       </c>
       <c r="F4" t="n">
-        <v>74</v>
+        <v>164</v>
       </c>
       <c r="G4" t="n">
-        <v>49</v>
+        <v>106.5</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
@@ -708,18 +756,18 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>DER_A.CC:56/74</t>
+          <t>DER_D.CC120164-C</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>ISO_CC09T3H</t>
+          <t>ISO_CC1204H</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>CC09T3H</t>
+          <t>CC1204H</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -737,7 +785,7 @@
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -746,12 +794,26 @@
         <is>
           <t>2019 / DEREK Металлорежущий инструмент и оснастка 2019 RUS_Ver.1.01</t>
         </is>
+      </c>
+      <c r="V4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" t="n">
+        <v>100.41</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>8231</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AACC90130</t>
+          <t>DACC120164-C</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -761,16 +823,16 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>22.6</v>
+        <v>29.7</v>
       </c>
       <c r="E5" t="n">
-        <v>90</v>
+        <v>12</v>
       </c>
       <c r="F5" t="n">
-        <v>130</v>
+        <v>164</v>
       </c>
       <c r="G5" t="n">
-        <v>82</v>
+        <v>106.5</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
@@ -779,7 +841,7 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>DER_A.CC:90/130</t>
+          <t>DER_D.CC120164-C</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -818,11 +880,25 @@
           <t>2019 / DEREK Металлорежущий инструмент и оснастка 2019 RUS_Ver.1.01</t>
         </is>
       </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="n">
+        <v>100.41</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>8231</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ABCC2026</t>
+          <t>AACC3645</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -832,16 +908,16 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>11.85</v>
+        <v>11.7</v>
       </c>
       <c r="E6" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="F6" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="G6" t="n">
-        <v>17.7</v>
+        <v>32</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
@@ -850,7 +926,7 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>DER_A.CC:20/25</t>
+          <t>DER_A.CC:36/44</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -879,7 +955,7 @@
       </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -888,6 +964,20 @@
         <is>
           <t>2019 / DEREK Металлорежущий инструмент и оснастка 2019 RUS_Ver.1.01</t>
         </is>
+      </c>
+      <c r="V6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" t="n">
+        <v>71.11</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>5829.16</v>
       </c>
     </row>
   </sheetData>
